--- a/docs/research/integrated-product-106/Experience/cases/NORTHLINE-04/NORTHLINE-04_Evidence_Workbook.xlsx
+++ b/docs/research/integrated-product-106/Experience/cases/NORTHLINE-04/NORTHLINE-04_Evidence_Workbook.xlsx
@@ -40,7 +40,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -117,6 +117,13 @@
       <color rgb="00121A2E"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Archivo"/>
+      <b val="1"/>
+      <color rgb="008F5A28"/>
+      <sz val="11"/>
+      <u val="single"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -154,7 +161,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
@@ -198,6 +205,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -724,17 +732,6 @@
           <t>UNAPPROVED · fictional source review · no professional decisions or approvals recorded</t>
         </is>
       </c>
-      <c r="B3" s="3" t="n"/>
-      <c r="C3" s="3" t="n"/>
-      <c r="D3" s="3" t="n"/>
-      <c r="E3" s="3" t="n"/>
-      <c r="F3" s="3" t="n"/>
-      <c r="G3" s="3" t="n"/>
-      <c r="H3" s="3" t="n"/>
-      <c r="I3" s="3" t="n"/>
-      <c r="J3" s="3" t="n"/>
-      <c r="K3" s="3" t="n"/>
-      <c r="L3" s="3" t="n"/>
     </row>
     <row r="4" ht="19" customHeight="1"/>
     <row r="5" ht="19" customHeight="1">
@@ -743,60 +740,29 @@
           <t>unique current source versions</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
       <c r="E5" s="4" t="inlineStr">
         <is>
           <t>unresolved source versions</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>proposed target rows</t>
         </is>
       </c>
-      <c r="J5" s="5" t="n"/>
-      <c r="K5" s="5" t="n"/>
-      <c r="L5" s="5" t="n"/>
     </row>
     <row r="6" ht="19" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-      <c r="D6" s="5" t="n"/>
       <c r="E6" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
-      <c r="H6" s="5" t="n"/>
       <c r="I6" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="J6" s="5" t="n"/>
-      <c r="K6" s="5" t="n"/>
-      <c r="L6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="19" customHeight="1">
-      <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="n"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
-      <c r="H7" s="5" t="n"/>
-      <c r="I7" s="5" t="n"/>
-      <c r="J7" s="5" t="n"/>
-      <c r="K7" s="5" t="n"/>
-      <c r="L7" s="5" t="n"/>
-    </row>
+    </row>
+    <row r="7" ht="19" customHeight="1"/>
     <row r="8" ht="19" customHeight="1"/>
     <row r="9" ht="19" customHeight="1">
       <c r="A9" s="7" t="inlineStr">
@@ -837,36 +803,10 @@
           <t>Confirm the applicable N-S01 schedule revision through professional review and separate schedule approval; preserve both source assertions.</t>
         </is>
       </c>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
-      <c r="J14" s="12" t="n"/>
-      <c r="K14" s="12" t="n"/>
-      <c r="L14" s="12" t="n"/>
-    </row>
-    <row r="15" ht="19" customHeight="1">
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="12" t="n"/>
-      <c r="J15" s="12" t="n"/>
-      <c r="K15" s="12" t="n"/>
-      <c r="L15" s="12" t="n"/>
-    </row>
-    <row r="16" ht="19" customHeight="1">
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="19" customHeight="1">
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="12" t="n"/>
-    </row>
+    </row>
+    <row r="15" ht="19" customHeight="1"/>
+    <row r="16" ht="19" customHeight="1"/>
+    <row r="17" ht="19" customHeight="1"/>
     <row r="18" ht="19" customHeight="1"/>
     <row r="19" ht="19" customHeight="1">
       <c r="A19" s="13" t="inlineStr">
@@ -874,40 +814,18 @@
           <t>Findings and review requests</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
       <c r="E19" s="13" t="inlineStr">
         <is>
           <t>Browse supplied Owner WBS</t>
         </is>
       </c>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
-      <c r="H19" s="5" t="n"/>
       <c r="I19" s="13" t="inlineStr">
         <is>
           <t>Follow each source record</t>
         </is>
       </c>
-      <c r="J19" s="5" t="n"/>
-      <c r="K19" s="5" t="n"/>
-      <c r="L19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="19" customHeight="1">
-      <c r="A20" s="5" t="n"/>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
-      <c r="H20" s="5" t="n"/>
-      <c r="I20" s="5" t="n"/>
-      <c r="J20" s="5" t="n"/>
-      <c r="K20" s="5" t="n"/>
-      <c r="L20" s="5" t="n"/>
-    </row>
+    </row>
+    <row r="20" ht="19" customHeight="1"/>
     <row r="21" ht="19" customHeight="1"/>
     <row r="22" ht="19" customHeight="1">
       <c r="A22" s="13" t="inlineStr">
@@ -915,28 +833,13 @@
           <t>Open original source files</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
       <c r="E22" s="13" t="inlineStr">
         <is>
           <t>Counting and authority</t>
         </is>
       </c>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
-      <c r="H22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="19" customHeight="1">
-      <c r="A23" s="5" t="n"/>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
-      <c r="H23" s="5" t="n"/>
-    </row>
+    </row>
+    <row r="23" ht="19" customHeight="1"/>
     <row r="24" ht="19" customHeight="1"/>
     <row r="25" ht="19" customHeight="1">
       <c r="A25" s="14" t="inlineStr">
@@ -1079,7 +982,7 @@
           <t>Original evidence route</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="17" t="inlineStr">
         <is>
           <t>← START HERE</t>
         </is>
@@ -1236,7 +1139,7 @@
           <t>Actual parent</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="17" t="inlineStr">
         <is>
           <t>← START HERE</t>
         </is>
@@ -1477,7 +1380,7 @@
           <t>Recorded classification</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="17" t="inlineStr">
         <is>
           <t>← START HERE</t>
         </is>
@@ -2252,7 +2155,7 @@
           <t>Located blocks</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>← START HERE</t>
         </is>
@@ -2437,7 +2340,7 @@
           <t>Value / boundary</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="17" t="inlineStr">
         <is>
           <t>← START HERE</t>
         </is>
@@ -2515,6 +2418,8 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
